--- a/data/evaluation/historical_case_benchmark.xlsx
+++ b/data/evaluation/historical_case_benchmark.xlsx
@@ -1241,17 +1241,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>NEWS_015</t>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>在西爪哇省苏邦工业园区建设印尼工厂，总投资约 10 亿美元，规划年产能 15 万辆，计划 2025 年底前竣工；与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
+          <t>在西爪哇省苏邦 Smartpolitan 工业园区建设印尼工厂，投资约 16 万亿印尼盾（约 10 亿美元），最大年产能 15 万辆；2026-09-03 正式投产启用，为比亚迪全球第 13 座整车工厂。与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>本地生产规避印尼整车进口关税，获得电动车补贴资格。 / 截至 2025 年报道仍处于建设阶段，预计 2025 年底竣工（结果待验证）。 / 以本地生产进入印尼市场，直接与日系品牌竞争。 / 电池与关键零部件初期由中国供应，形成中印尼跨境供应链。</t>
+          <t>本地生产规避印尼整车进口关税并满足本地化率（TKDN）要求，保住电动车激励资格；工厂投资约 16 万亿印尼盾。 / 2026-09-03 正式投产，最大年产能 15 万辆，投产后实际产量约 1 万辆/月；启用仪式同场下线印尼本地生产的第 10 万辆整车。 / 2026-09 起停止整车进口、全面转为本地生产，以本地化进入印尼市场并与日系品牌竞争。 / 电池与关键零部件初期由中国供应，形成中印尼跨境供应链。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>计划在越南北部（太原省）投资约 40 亿美元建设芯片测试与封装工厂，分阶段实施；中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
+          <t>计划在越南北部（太原省）投资约 15 亿美元建设芯片测试与封装工厂（已见报道的初始项目）。媒体另称可能追加约 25 亿美元的第二工厂投资——该项为条件性后续计划，尚未确认实施，不能与初始项目合并为单一'约 40 亿美元'已确定项目。中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>越南人工与土地成本低于韩国，但芯片封测对工程师与配套要求高，初期效率受限。 / 截至 2026 年仍为投资计划阶段（结果待验证）。 / 分散对单一国家出口管制的暴露。 / 封装测试外移，但前道晶圆制造仍集中在韩国与中国。</t>
+          <t>越南人工与土地成本低于韩国，但芯片封测对工程师与配套要求高，初期效率受限。 / 截至 2026 年 10 月仍为投资计划阶段，未见公司正式公告确认实施或落地产能。 / 分散对单一国家出口管制的暴露。 / 封装测试外移，但前道晶圆制造仍集中在韩国与中国。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2025 年 7 月及 12 月，富士康两度从印度工厂撤回中国大陆工程师与技术团队，部分产能与订单回流中国大陆；印度的组装布局并未取消，但节奏明显放缓。</t>
+          <t>2025 年 7 月及 12 月，富士康两度要求/撤回其印度工厂的中国大陆工程师与技术团队（彭博社等报道）。印度的组装布局并未取消，但推进节奏明显放缓。注：现有证据仅支持'工程团队撤回、工程支持减弱'，不足以证明订单或产能已实际回流中国。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；中国基地继续承担高难度工序。 / 印度工厂良率与产能爬坡受阻，中国大陆产能利用率回升。 / 对美出口仍依托中国与东南亚双通道。 / 验证了'关键工序与工程能力仍在中国'的结构性依赖。</t>
+          <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；高难度工序仍由中国基地承担。 / 印度工厂工程支持减弱、本地良率与产能爬坡受阻（有报道支持）；中国大陆产能利用率是否回升尚无直接证据，待验证。 / 对美出口仍依托中国与东南亚双通道。 / 印证了'关键工序与工程能力仍依赖中国'的结构性依赖（有报道支持）。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">

--- a/data/evaluation/historical_case_benchmark.xlsx
+++ b/data/evaluation/historical_case_benchmark.xlsx
@@ -1890,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2020,11 +2020,28 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>是否进入 RAG 语料</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>否（held-out）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>案例是评测答案键，故意不进入知识库，避免答案泄漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>已知局限</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>结果字段多来自媒体转述；4 个案例结果尚未发生；行业级案例 RETURN_003 无单一企业数据</t>
         </is>

--- a/data/evaluation/historical_case_benchmark.xlsx
+++ b/data/evaluation/historical_case_benchmark.xlsx
@@ -12,7 +12,7 @@
     <sheet name="QA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Benchmark'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Benchmark'!$A$1:$O$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,11 +459,14 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -504,30 +507,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>evidence_sources</t>
+          <t>related_evidence_ids</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>evidence_rationale</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>external_source_refs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>actual_decision</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>outcome</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>key_factors</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>expected_risks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>decision_type</t>
         </is>
@@ -571,30 +584,40 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>R1 美国对华电动车关税/欧盟反补贴(EU_003)是出海触发；R3 中美自泰进口整车与电池数据(TRD_001)显示泰国通道；R4 光模块厂泰国产能(CASE_004)提供同去向类比；R3 全球EV格局(IEA_001)；R2 泰国物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>NEWS_001</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>2022-09 与 WHA 签约，在泰国罗勇府建全资乘用车工厂；2024-07-04 竣工投产，年产能约 15 万辆，投资约 350 亿泰铢（约 69.5 亿元人民币）。中国产能保留并继续扩产。</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>本地化生产规避东盟整车进口税，叠加泰国 BOI 税收优惠降低综合税负；但泰国本地零部件配套不足，短期单位成本高于中国。 / 开工到投产仅 16 个月，创中国车企在泰最快投产纪录；第 800 万辆新能源汽车在泰国工厂下线。 / 直接覆盖泰国及东盟右舵市场，从整车出口转为本地供应，显著降低准入壁垒。 / 关键零部件初期仍依赖中国进口，本地供应链配套率低，形成新的跨境物流依赖。</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure; 美国对华电动车加征关税、欧盟反补贴调查，出口关税壁垒上升；泰国对本地组装提供 BOI 优惠。</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -638,30 +661,40 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>R1 关税与泰国本地化要求为触发；R2 美国自泰进口整车/电池(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>NEWS_002; COMPANY_REPORT_001</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>在泰国罗勇府建设整车工厂，2025-05-16 竣工投产，全球累计第 2859 万辆（深蓝 S05）在泰下线；中国产能保留。</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>获得泰国 BOI 优惠与 EV3.5 补贴资格，降低进入东盟的单位成本。 / 2026-09 公司确认罗勇工厂已建成投产并具备整车本地化生产能力。 / 从整车出口转为本地生产，满足泰国本地化要求，保住补贴资格。 / 零部件本地化配套率仍在爬坡，初期依赖中泰跨境供应。</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>market_access; 泰国 EV3.5 补贴政策要求本地生产，才能享受补贴与关税优惠。</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -705,30 +738,40 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口电池数据(TRD_001)与中国对越中间品出口(TRD_003)共同刻画越南通道；R3 中国电池厂全球份额(SNE_001)；R2 物流绩效(WB_001)；R4 东南亚建厂类比(CASE_007)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>NEWS_003; NEWS_004</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>与 Vingroup 旗下 VinES 合资（国轩 51% / VinES 49%）在越南河静经济开发区建越南首座 LFP 电池工厂，一期规划年产能 5GWh；2026-07 公司披露德国、越南、印尼、泰国四大海外基地已陆续投产，越南基地为亚洲首条 LFP 电芯工厂。</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>就近配套降低物流与关税成本；越南人工与土地成本低于中国。 / 四大海外基地陆续投产，越南基地定位为亚洲首个 LFP 电芯工厂。 / 绑定 VinFast 这一本地整车客户，进入越南及东盟供货体系。 / 正负极等关键材料仍从中国输入，越南基地形成'中国材料—越南电芯'的跨境结构。</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>market_access; 越南 VinFast 本地化生产需要就近电池配套，越南对电池进口设有本地化要求。</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -772,30 +815,40 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自马进口电池(TRD_001)+中国对马中间品出口(TRD_003)；R4 马来西亚工厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>NEWS_005</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>在马来西亚吉打州居林县建设海外工厂，二期于 2026 年 2 月投产运营，建筑面积约 60 万平方米，系公司首个海外大型锂电厂房项目，形成年产约 6.8 亿只圆柱电池产能；同时推进匈牙利、美国、印尼项目，中国产能保留。</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>马来西亚产能提升出口业务规避税率的能力，降低对美出口关税成本。 / 二期投产形成规模化圆柱电池产能，海外交付能力显著提升。 / 马来西亚基地作为面向欧美客户的出口枢纽，缓解关税与本地化压力。 / 设备与材料初期仍由中国输入，形成'中国材料—马来西亚制造—欧美市场'链条。</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure; 对美出口关税与'去中国化'供应链要求，迫使企业在东南亚布局产能以规避税率。</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -839,30 +892,40 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口(TRD_001)+对越中间品出口(TRD_003)；R4 东南亚建厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>NEWS_006; NEWS_007</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2024-07-15 公告拟通过下属子公司香港欣威设立越南锂威有限公司，投建越南锂威消费类锂电池工厂项目，投资总额不超过 20 亿元人民币；2026-08 公司表示越南消费类电芯生产基地预计 2026 年底投产。中国产能保留。</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>越南基地降低对美出口关税暴露，但前期资本开支与本地配套成本较高。 / 截至 2026-08 仍在建设期，预计 2026 年底投产（结果尚待验证）。 / 满足欧美消费电子客户对非中国产能的采购要求。 / 材料仍由中国供应，越南以电芯制造环节为主。</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure; 美国对华加征关税及客户'中国+1'采购要求，推动消费类电芯产线外移。</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -906,30 +969,40 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟反补贴税(EU_003)抬高欧洲出口成本；R2 美国自泰进口(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流(WB_001)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>NEWS_008</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>在泰国春武里府是拉差市建设电池工厂（模组 PACK + 电芯），2024-02-28 正式投产并批量交付，配套长城欧拉、合众/哪吒等中国车企在泰车型；当年计划交付超 2 万套 PACK；中国产能保留。</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>本地 PACK 组装降低关税与物流成本，投资规模小于整线电芯厂。 / 2024-02 投产并批量交付，产能按订单爬坡。 / 绑定泰国本地中国品牌整车客户，进入泰国本地供应体系。 / 电芯/材料仍从中国输入，泰国仅承担模组与 PACK 环节。</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>market_access; 跟随中国整车客户出海，满足泰国本地化电池配套要求。</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -973,30 +1046,40 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼贸易政策审议包含镍下游化政策(WTO_004)；R1 中国对印尼中间品出口(TRD_003)；R3 电池材料格局(SNE_001)；R2 印尼物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>NEWS_009</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>自 2018 年起在印尼布局镍钴资源，依托青山系莫罗瓦利与纬达贝工业园建设红土镍矿湿法冶炼项目（华越 6 万吨、华飞 12 万吨镍金属量等），2024-04 年产 12 万吨镍钴湿法项目达产；2026-01 表示 Pomalaa 年产 12 万吨镍金属量湿法项目预计 2026 年底建成投产。中国冶炼与材料产能保留。</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>印尼湿法冶炼的万吨镍投资约为世界同类项目的三分之一，原料自给降低成本。 / 多个湿法项目达产，关键原料自供比例显著提升。 / 以印尼镍产品供应中国及全球前驱体客户，绕开原矿出口禁令。 / 形成'印尼资源—中国材料'的双向依赖，海外上游集中度上升带来新的地缘风险。</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>supplier_issue; 印尼 2020 年起禁止镍原矿出口，要求就地冶炼；下游电池需求推升镍资源安全诉求。</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1040,30 +1123,40 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化与本地化要求(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>NEWS_010; NEWS_011</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>在印尼建设北莫罗瓦利、莫罗瓦利、纬达贝三大原料基地，2024-04 三基地已投产；2026-01 莫罗瓦利中青新能源二期全面投产（首炉冰镍产出），在建及建成资源粗炼端产能约 12.5 万金属吨。中国前驱体产能保留。</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>自供原料比例提升，降低外购镍价波动影响。 / 三基地投产、二期冰镍产线投料试产成功，产能持续释放。 / 以自产镍资源支撑中国及海外前驱体客户供货。 / 海外上游集中于印尼，单一国家集中度风险上升。</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>supplier_issue; 印尼原矿出口禁令 + 客户对低碳、可追溯镍的需求。</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1107,30 +1200,40 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)+CRMA(EU_002)构成匈牙利建厂的合规与准入约束；R3 宁德时代全球份额(SNE_001)与EV格局(IEA_001)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>NEWS_012; NEWS_013</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>在匈牙利德布勒森建设欧洲第二座电池工厂，投资约 73.4 亿欧元（匈牙利史上最大外资项目之一），规划总产能 100GWh；2022-08 宣布，2023 年夏季首座电芯厂房动工，2026-08 取得厂房使用许可，2026-09-22 启动试生产；德国工厂与中国基地继续运营。</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>欧洲本地生产规避电池进口关税并获得本地补贴，但欧洲能源与人工成本显著高于中国。 / 2026-09 进入试生产阶段，尚未规模量产（结果待验证）。 / 就近供应奔驰等欧洲客户，满足欧盟本地化与合规要求。 / 正极、负极、电解液等仍需中国及亚洲供应，形成'中国材料—欧洲电芯'结构。</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>regulation_change; 欧盟电池法规与本地化含量要求，叠加欧洲整车客户对就近供货的需求。</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1174,30 +1277,40 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化/本地化(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 份额与格局(SNE_001,IEA_001)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>NEWS_014</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>由子公司普勤时代（CBL）、印尼国有矿业公司 ANTAM 与印尼电池公司 IBC 组成联合体，2025-06-29 在西爪哇省卡拉旺产业新城动工建设'从镍矿开采—冶炼—前驱体—电池制造—回收'一体化项目，总投资近 60 亿美元，电池产能规划 15GWh，可满足约 25–30 万辆汽车需求；中国产能保留。</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>一体化布局降低原料与中间品跨境成本，但前期资本开支巨大。 / 2025-06 动工，处于建设期（结果待验证）。 / 进入印尼本地供应链并满足资源下游化要求，辐射东南亚市场。 / 把镍资源与电池制造绑定在印尼，减少对中国中间品运输的依赖，但新增单一国家集中度。</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>regulation_change; 印尼'下游化'政策要求镍矿就地加工并延伸至电池产业链。</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1241,30 +1354,40 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>R2 印尼本地化政策(WTO_004)直接对应'转为全本地生产'的结果；R3 格局(IEA_001,SNE_001)；R1 中间品出口(TRD_003)+欧盟反补贴(EU_003)说明多地区布局动因</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>NEWS_015; NEWS_024; NEWS_025</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>在西爪哇省苏邦 Smartpolitan 工业园区建设印尼工厂，投资约 16 万亿印尼盾（约 10 亿美元），最大年产能 15 万辆；2026-09-03 正式投产启用，为比亚迪全球第 13 座整车工厂。与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>本地生产规避印尼整车进口关税并满足本地化率（TKDN）要求，保住电动车激励资格；工厂投资约 16 万亿印尼盾。 / 2026-09-03 正式投产，最大年产能 15 万辆，投产后实际产量约 1 万辆/月；启用仪式同场下线印尼本地生产的第 10 万辆整车。 / 2026-09 起停止整车进口、全面转为本地生产，以本地化进入印尼市场并与日系品牌竞争。 / 电池与关键零部件初期由中国供应，形成中印尼跨境供应链。</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure; 印尼对整车进口征收高关税并推行电动车本地化要求，2023-05 与印尼政府签署投资谅解备忘录。</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1308,30 +1431,40 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>R1 美国对东南亚四国光伏反规避终裁(DOC_001)是该案例决策的直接触发；R4 同调查'已规避/未规避'案例(CASE_002,CASE_003)；R2 美国光伏进口数据(TRD_002)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>NEWS_016</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>保持中国核心产能，同时在马来西亚（对美/欧核心出口枢纽）、越南（一体化产能）与美国本土布局成熟产能，形成'中国 + 东南亚 + 北美'的三地结构。</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>马来西亚基地不受本轮关税影响，成为对美欧出口枢纽；美国本土产能直接受益于关税保护。 / 多地产能并行，具体产能与利用率需以公司财报核实。 / 通过多地产能规避单一市场的关税与反规避风险。 / 硅片、电池等中间品仍在区域内跨境流动，东南亚基地对中国中间品存在依赖。</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>tariff_pressure; 美国对东南亚光伏组件的双反/反规避认定，以及美国本土制造激励，要求产能进一步分散。</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1375,30 +1508,40 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD 投资报告把三星/富士康类外迁作为 FDI 案例(UNCTAD_001)；R1 对越中间品出口(TRD_003)；R2 越南物流绩效(WB_001)；R3 IMF 对水平型 FDI 的举例(IMF_001)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>NEWS_017</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>计划在越南北部（太原省）投资约 15 亿美元建设芯片测试与封装工厂（已见报道的初始项目）。媒体另称可能追加约 25 亿美元的第二工厂投资——该项为条件性后续计划，尚未确认实施，不能与初始项目合并为单一'约 40 亿美元'已确定项目。中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>越南人工与土地成本低于韩国，但芯片封测对工程师与配套要求高，初期效率受限。 / 截至 2026 年 10 月仍为投资计划阶段，未见公司正式公告确认实施或落地产能。 / 分散对单一国家出口管制的暴露。 / 封装测试外移，但前道晶圆制造仍集中在韩国与中国。</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>geopolitical_uncertainty; 中美科技与关税摩擦，以及 AI 驱动的存储芯片短缺，推动封装测试产能向第三国分散。</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>多地区混合布局</t>
         </is>
@@ -1442,30 +1585,40 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>R4 大旺金属'订单转移后回流'案例(CASE_001)是直接类比；R1 对马中间品出口与配套依赖(TRD_003)；R2 物流成本(WB_001)；R3 行业格局(SNE_001)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>COMPANY_FILING_001; NEWS_018</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2026-05-22 董事会审议通过《关于终止在马来西亚投资建设锂电池隔离膜项目的议案》，终止原计划约 20 亿元的马来西亚隔膜项目，资源回投国内，优化资源配置、降低风险。</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>避免在行业下行期投入 20 亿元海外资本开支，节省资金；但失去东南亚本地化产能抓手。 / 国内产能继续承担全球交付，海外扩张暂停。 / 对海外客户仍以中国出口方式交付，关税暴露未消除。 / 海外供应链布局收缩，对单一中国基地的依赖上升。</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>cost_change; 外部市场环境及行业竞争格局发生变化（隔膜价格下行、行业产能过剩、海外建厂成本高于预期）。</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
@@ -1509,30 +1662,40 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD_001 直接引用路透'富士康印度 iPhone 出口'报道（同源提示）；R2 印度贸易政策审议与关税(WTO_002,WTO_003)；R4 回流类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>NEWS_019; NEWS_020</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2025 年 7 月及 12 月，富士康两度要求/撤回其印度工厂的中国大陆工程师与技术团队（彭博社等报道）。印度的组装布局并未取消，但推进节奏明显放缓。注：现有证据仅支持'工程团队撤回、工程支持减弱'，不足以证明订单或产能已实际回流中国。</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>撤回技术人员降低了印度工厂的爬坡效率，短期成本上升；高难度工序仍由中国基地承担。 / 印度工厂工程支持减弱、本地良率与产能爬坡受阻（有报道支持）；中国大陆产能利用率是否回升尚无直接证据，待验证。 / 对美出口仍依托中国与东南亚双通道。 / 印证了'关键工序与工程能力仍依赖中国'的结构性依赖（有报道支持）。</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>geopolitical_uncertainty; 印度本地化配套与技术能力不足，导致良率与交付不达预期。</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
@@ -1576,30 +1739,40 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>R4 行业层面回流的核心类比是 CASE_001（大旺金属，订单外移印度后回流）；R2 物流与配套成本(WB_001)；R1 关税背景(TRD_001)；R3 美国供应链调查(KPMG_001)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>REUTERS_001; NEWS_023</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>部分跨国企业将订单与产能重新回流中国，同时保留东南亚既有布局，形成'中国为主 + 东南亚保留'的混合结构。</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>回流后综合成本下降，关税优势部分让位于运转效率。 / 中国工厂产能利用率回升，交付稳定性改善。 / 对美出口仍需应对关税，部分通过第三国转运与产品结构调整解决。 / 印证中国在配套完整度上的不可替代性，'China+1'演变为'China+1 但中国仍是主基地'。</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>cost_change; 东南亚等地综合成本高于预期 + 电力等基础设施不稳定，抵消关税收益。</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>提高中国生产比例</t>
         </is>
@@ -1643,37 +1816,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)是收缩欧洲布局的直接约束；R4 回流/收缩类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2024-05 取消勃兰登堡州电芯超级工厂计划，2024-10 宣布停建德国工厂、终止欧洲子公司运营（自 2025 年 1 月起关闭欧洲业务），资源集中于中国与泰国等已投产基地。</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>停止约 300 亿元级别的海外投资计划，避免持续亏损。 / 欧洲产能归零，中国与泰国基地继续运营。 / 退出欧洲本地化生产，欧洲市场改以出口方式服务。 / 海外布局从'欧洲 + 东南亚'收缩为'东南亚'。</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>cost_change; 欧洲销售疲软 + 经济挑战 + 融资困难，海外扩张的投入产出不成立。</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>维持现有海外布局（收缩新增）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1684,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1797,83 +1980,100 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>evidence_sources</t>
+          <t>related_evidence_ids</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>证据来源（related_evidence_ids + 链接）</t>
+          <t>证据库绑定（Task 1 的 49 条证据，附绑定依据）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NEWS_001</t>
+          <t>TRD_001; EU_003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>actual_decision</t>
+          <t>external_source_refs</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>真实决策</t>
+          <t>外部新闻来源编号（见 case_database 的 Evidence Index）</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>泰国罗勇府建厂，2024-07 投产</t>
+          <t>NEWS_001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>actual_decision</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>后续结果（成本 / 生产 / 准入 / 供应链）</t>
+          <t>真实决策</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>降低准入壁垒，但零部件仍依赖中国</t>
+          <t>泰国罗勇府建厂，2024-07 投产</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>key_factors</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>关键因素</t>
+          <t>后续结果（成本 / 生产 / 准入 / 供应链）</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>tariff_pressure; market_access</t>
+          <t>降低准入壁垒，但零部件仍依赖中国</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>key_factors</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>关键因素</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>tariff_pressure; market_access</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>related_risks</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>相关风险（Task 1 六类）</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Trade Risk; Market Access Risk</t>
         </is>
@@ -1890,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1945,7 +2145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>全部绑定 related_evidence_ids，来源见 case_database 的 Evidence Index</t>
+          <t>外部来源编号见 external_source_refs（映射到 case_database 的 Evidence Index，含 outlet/标题/日期/URL）</t>
         </is>
       </c>
     </row>
@@ -2037,11 +2237,130 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>证据库绑定</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>related_evidence_ids 已改为 Task 1 证据库内的真实 ID，逐条附绑定依据（R1触发/R2目的地/R3行业/R4类比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>held-out 校验</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>语料 49 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>语料泄漏检查（逐字）</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/check_case_leakage.py：17/17 通过，最高逐字重合 1.0%（10 字滑窗，阈值 5%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>隔离校验复跑</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>check_case_leakage.py</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>.venv/bin/python backend/scripts/check_case_leakage.py —— 退出码 0 表示案例 ID / 来源 URL / 逐字重合 / 证据绑定四项全过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>语料背景重合（已登记）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>4 处</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001/PLUS1_003 经 IEA_001 的 OEM 名单；PLUS1_004 经 DOC_001 的光伏反规避语境；PLUS1_005 经 IMF_001 的 FDI 举例；RETURN_002 经 UNCTAD_001 引用的路透稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>同源提示</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>外部来源为路透报道，而语料 UNCTAD_001 引用了同一系列路透稿；属背景级同源，评测时需知悉</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>通用吸引子</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>语料 CASE_001（大旺金属回流）出现在全部 17 个案例的 Top-5，是 Task 6 false positive 的来源之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>已知局限</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>结果字段多来自媒体转述；4 个案例结果尚未发生；行业级案例 RETURN_003 无单一企业数据</t>
         </is>

--- a/data/evaluation/historical_case_benchmark.xlsx
+++ b/data/evaluation/historical_case_benchmark.xlsx
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>证据库绑定（Task 1 的 49 条证据，附绑定依据）</t>
+          <t>证据库绑定（Task 1 的 53 条证据，附绑定依据）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>语料 49 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
+          <t>语料 53 篇文档 ID 中无 RELOC_*/PLUS1_*/RETURN_*；17 个案例来源 URL 与语料 URL 零重合</t>
         </is>
       </c>
     </row>
